--- a/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9828FF02-D57B-4323-8483-F339B8A0CA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2097308E-CC03-4618-920C-6465E8EA3EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-2010" windowWidth="28995" windowHeight="15675" activeTab="6" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="217">
   <si>
     <t>Result</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Alcohol Tax</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -390,6 +387,315 @@
   </si>
   <si>
     <t>This is in QA and Demo but not in Production</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:20:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:21:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:22:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:24:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:25:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:26:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:27:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:29:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:30:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:31:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:32:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:33:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:35:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:36:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:37:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:38:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:39:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:41:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:42:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:43:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:44:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:45:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:46:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:48:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:49:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:50:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:52:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:53:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:54:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:55:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:56:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:58:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 21:59:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:00:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:01:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:05:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:06:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:08:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:09:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:10:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:11:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:12:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:13:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:15:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:16:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:17:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:18:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:19:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:20:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:21:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:23:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:24:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:25:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:26:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:27:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:28:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:30:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:31:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:32:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:33:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:34:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:35:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:36:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:38:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:39:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:40:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:41:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:42:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:43:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:45:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:46:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:47:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:48:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:49:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:50:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:51:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:53:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:54:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:55:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:56:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:57:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:58:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 22:59:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:01:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:03:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:04:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:06:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:07:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:09:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:10:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:11:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:13:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:14:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:15:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:16:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:17:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:18:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:20:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 29 23:21:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 11:23:13 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -765,23 +1071,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,20 +1110,24 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -826,23 +1136,27 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -851,23 +1165,27 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>119</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -876,26 +1194,30 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -904,26 +1226,30 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>121</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -932,26 +1258,30 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>122</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -960,19 +1290,42 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -988,21 +1341,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.6328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.1796875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.36328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,402 +1372,478 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>124</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>127</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>128</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>129</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8"/>
-      <c r="B8"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>130</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9"/>
-      <c r="B9"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10"/>
-      <c r="B10"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>132</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11"/>
-      <c r="B11"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12"/>
-      <c r="B12"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>134</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="1" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="1" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="1" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="1" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="1" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20"/>
-      <c r="B20"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>141</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21"/>
-      <c r="B21"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1428,20 +1857,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.453125" style="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
     <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1464,17 +1893,21 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1483,20 +1916,24 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -1505,17 +1942,21 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
@@ -1524,20 +1965,24 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
@@ -1546,20 +1991,24 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
@@ -1568,20 +2017,24 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>148</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
@@ -1590,13 +2043,13 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1611,21 +2064,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1796875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
+    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1645,29 +2098,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -1675,18 +2132,22 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1">
-        <v>2024</v>
+      <c r="F2" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -1694,21 +2155,25 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1">
-        <v>2024</v>
+      <c r="F3" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -1716,21 +2181,25 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>2024</v>
+      <c r="F4" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>216</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -1738,21 +2207,25 @@
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1">
-        <v>2024</v>
+      <c r="F5" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>152</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -1760,21 +2233,25 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1">
-        <v>2024</v>
+      <c r="F6" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>153</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -1782,18 +2259,22 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>2023</v>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8"/>
-      <c r="B8"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -1801,21 +2282,25 @@
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
-        <v>2023</v>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9"/>
-      <c r="B9"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>155</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
@@ -1823,21 +2308,25 @@
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1">
-        <v>2023</v>
+      <c r="F9" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10"/>
-      <c r="B10"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>156</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -1845,21 +2334,25 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1">
-        <v>2023</v>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11"/>
-      <c r="B11"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" t="s">
+        <v>157</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>15</v>
@@ -1867,21 +2360,25 @@
       <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1">
-        <v>2023</v>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12"/>
-      <c r="B12"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>158</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>15</v>
@@ -1889,18 +2386,22 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1">
-        <v>2022</v>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13"/>
-      <c r="B13"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
+      </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>15</v>
@@ -1908,21 +2409,25 @@
       <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
-        <v>2022</v>
+      <c r="F13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14"/>
-      <c r="B14"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" t="s">
+        <v>160</v>
+      </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>15</v>
@@ -1930,21 +2435,25 @@
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1">
-        <v>2022</v>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15"/>
-      <c r="B15"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>161</v>
+      </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>15</v>
@@ -1952,21 +2461,25 @@
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1">
-        <v>2022</v>
+      <c r="F15" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16"/>
-      <c r="B16"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>162</v>
+      </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>15</v>
@@ -1974,46 +2487,54 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1">
-        <v>2022</v>
+      <c r="F16" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18"/>
-      <c r="B18"/>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>164</v>
+      </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>15</v>
@@ -2021,24 +2542,28 @@
       <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="1">
-        <v>2025</v>
+      <c r="F18" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19"/>
-      <c r="B19"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>165</v>
+      </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>15</v>
@@ -2046,24 +2571,28 @@
       <c r="E19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="1">
-        <v>2025</v>
+      <c r="F19" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20"/>
-      <c r="B20"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
+        <v>166</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>15</v>
@@ -2071,90 +2600,106 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>2024</v>
+      <c r="F20" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24"/>
-      <c r="B24"/>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
+        <v>170</v>
+      </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>15</v>
@@ -2162,102 +2707,118 @@
       <c r="E24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="1">
-        <v>2025</v>
+      <c r="F24" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28"/>
-      <c r="B28"/>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" t="s">
+        <v>174</v>
+      </c>
       <c r="C28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>15</v>
@@ -2265,52 +2826,60 @@
       <c r="E28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="1">
-        <v>2025</v>
+      <c r="F28" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29"/>
-      <c r="B29"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
+        <v>175</v>
+      </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2024</v>
+        <v>34</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30"/>
-      <c r="B30"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>176</v>
+      </c>
       <c r="C30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>15</v>
@@ -2319,23 +2888,27 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31"/>
-      <c r="B31"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>177</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>15</v>
@@ -2343,24 +2916,28 @@
       <c r="E31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="1">
-        <v>2024</v>
+      <c r="F31" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32"/>
-      <c r="B32"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>178</v>
+      </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>15</v>
@@ -2368,90 +2945,106 @@
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
-        <v>2023</v>
+      <c r="F32" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36"/>
-      <c r="B36"/>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
+        <v>182</v>
+      </c>
       <c r="C36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>15</v>
@@ -2459,102 +3052,118 @@
       <c r="E36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F36" s="1">
-        <v>2024</v>
+      <c r="F36" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="F38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40"/>
-      <c r="B40"/>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
+        <v>186</v>
+      </c>
       <c r="C40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>15</v>
@@ -2562,52 +3171,60 @@
       <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="1">
-        <v>2024</v>
+      <c r="F40" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41"/>
-      <c r="B41"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>187</v>
+      </c>
       <c r="C41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2023</v>
+        <v>34</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42"/>
-      <c r="B42"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>188</v>
+      </c>
       <c r="C42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>15</v>
@@ -2615,24 +3232,28 @@
       <c r="E42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="1">
-        <v>2023</v>
+      <c r="F42" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43"/>
-      <c r="B43"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
+        <v>189</v>
+      </c>
       <c r="C43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>15</v>
@@ -2640,24 +3261,28 @@
       <c r="E43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="1">
-        <v>2023</v>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44"/>
-      <c r="B44"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>190</v>
+      </c>
       <c r="C44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>15</v>
@@ -2665,90 +3290,106 @@
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="1">
-        <v>2022</v>
+      <c r="F44" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="1" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K46" s="1" t="s">
+      <c r="F47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A47"/>
-      <c r="B47"/>
-      <c r="C47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48"/>
-      <c r="B48"/>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
+        <v>194</v>
+      </c>
       <c r="C48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>15</v>
@@ -2756,102 +3397,118 @@
       <c r="E48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F48" s="1">
-        <v>2023</v>
+      <c r="F48" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49"/>
-      <c r="B49"/>
-      <c r="C49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="1" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F49" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="F50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50"/>
-      <c r="B50"/>
-      <c r="C50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>197</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="F51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51"/>
-      <c r="B51"/>
-      <c r="C51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52"/>
-      <c r="B52"/>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" t="s">
+        <v>198</v>
+      </c>
       <c r="C52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>15</v>
@@ -2859,209 +3516,233 @@
       <c r="E52" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F52" s="1">
-        <v>2023</v>
+      <c r="F52" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L52" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F53" s="1" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56"/>
-      <c r="B56"/>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" t="s">
+        <v>201</v>
+      </c>
       <c r="C56" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57"/>
-      <c r="B57"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>116</v>
+      </c>
+      <c r="B57" t="s">
+        <v>202</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" t="s">
+        <v>203</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59" s="1" t="s">
+      <c r="L59" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3077,19 +3758,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.1796875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3109,17 +3790,21 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>206</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -3128,17 +3813,21 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>207</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -3147,17 +3836,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>208</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -3166,17 +3859,21 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>209</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -3185,17 +3882,21 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>210</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -3204,55 +3905,55 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
@@ -3266,19 +3967,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.1796875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3298,14 +3999,18 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>211</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -3314,17 +4019,21 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>212</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -3333,17 +4042,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>213</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -3352,17 +4065,21 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>214</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -3371,17 +4088,21 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>215</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -3390,10 +4111,10 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3404,17 +4125,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.453125" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.1796875" style="1" collapsed="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3431,36 +4152,40 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>205</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2097308E-CC03-4618-920C-6465E8EA3EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A018AB12-388A-459A-9CBD-C9998C00BAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="216">
   <si>
     <t>Result</t>
   </si>
@@ -395,307 +395,304 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:20:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:21:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:22:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:24:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:25:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:26:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:27:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:29:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:30:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:31:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:32:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:33:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:35:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:36:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:37:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:38:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:39:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:41:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:42:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:43:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:44:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:45:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:46:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:48:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:49:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:50:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:52:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:53:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:54:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:55:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:56:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:58:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 21:59:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:00:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:01:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:05:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:06:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:08:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:09:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:10:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:11:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:12:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:13:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:15:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:16:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:17:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:18:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:19:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:20:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:21:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:23:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:24:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:25:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:26:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:27:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:28:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:30:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:31:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:32:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:33:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:34:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:35:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:36:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:38:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:39:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:40:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:41:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:42:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:43:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:45:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:46:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:47:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:48:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:49:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:50:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:51:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:53:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:54:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:55:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:56:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:57:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:58:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 22:59:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:01:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:03:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:04:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:06:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:07:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:09:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:10:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:11:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:13:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:14:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:15:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:16:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:17:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:18:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:20:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 29 23:21:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 11:23:13 EDT 2026</t>
+    <t>Fri Jun 05 19:45:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:45:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:46:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:47:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:47:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:48:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:48:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:49:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:50:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:51:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:51:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:52:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:53:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:54:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:54:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:55:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:56:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:56:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:57:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:58:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:59:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:59:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:00:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:01:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:01:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:02:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:03:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:03:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:04:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:05:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:05:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:06:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:07:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:08:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:08:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:09:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:09:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:10:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:11:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:12:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:12:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:13:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:14:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:14:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:15:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:16:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:17:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:18:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:19:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:19:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:20:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:21:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:21:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:22:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:22:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:23:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:24:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:25:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:26:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:28:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:29:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:30:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:31:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:33:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:34:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:35:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:36:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:38:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:39:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:40:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:42:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:43:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:44:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:46:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:47:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:48:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:49:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:51:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:52:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:53:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:55:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:56:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:57:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:58:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:00:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:01:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:02:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:03:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:05:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:06:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:08:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:09:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:11:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:12:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:20:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:27:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:28:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:29:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:30:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 11:31:37 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1121,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1153,7 +1150,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1182,7 +1179,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1214,7 +1211,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1246,7 +1243,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1278,7 +1275,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1307,10 +1304,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1392,7 +1389,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1415,7 +1412,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1438,7 +1435,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1461,7 +1458,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1487,7 +1484,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1513,7 +1510,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1536,7 +1533,7 @@
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1559,7 +1556,7 @@
         <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1582,7 +1579,7 @@
         <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1605,7 +1602,7 @@
         <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1628,7 +1625,7 @@
         <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1651,7 +1648,7 @@
         <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1674,7 +1671,7 @@
         <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1697,7 +1694,7 @@
         <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1717,7 +1714,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1743,7 +1740,7 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1766,7 +1763,7 @@
         <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1805,10 +1802,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1825,10 +1822,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -1904,7 +1901,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1930,7 +1927,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1953,7 +1950,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1979,7 +1976,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2005,7 +2002,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2031,7 +2028,7 @@
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2121,7 +2118,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2144,7 +2141,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2170,7 +2167,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2196,7 +2193,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2450,7 +2447,7 @@
         <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2476,7 +2473,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2502,7 +2499,7 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2531,7 +2528,7 @@
         <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2560,7 +2557,7 @@
         <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2589,7 +2586,7 @@
         <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2612,7 +2609,7 @@
         <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2641,7 +2638,7 @@
         <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2670,7 +2667,7 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2696,7 +2693,7 @@
         <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2725,7 +2722,7 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2757,7 +2754,7 @@
         <v>115</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2786,7 +2783,7 @@
         <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2815,7 +2812,7 @@
         <v>115</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2847,7 +2844,7 @@
         <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2876,7 +2873,7 @@
         <v>115</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2905,7 +2902,7 @@
         <v>115</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2934,7 +2931,7 @@
         <v>115</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2957,7 +2954,7 @@
         <v>115</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -2986,7 +2983,7 @@
         <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3015,7 +3012,7 @@
         <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3041,7 +3038,7 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3070,7 +3067,7 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3102,7 +3099,7 @@
         <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3131,7 +3128,7 @@
         <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3160,7 +3157,7 @@
         <v>115</v>
       </c>
       <c r="B40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3192,7 +3189,7 @@
         <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3221,7 +3218,7 @@
         <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3250,7 +3247,7 @@
         <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3279,7 +3276,7 @@
         <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3302,7 +3299,7 @@
         <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3331,7 +3328,7 @@
         <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3360,7 +3357,7 @@
         <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3386,7 +3383,7 @@
         <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3415,7 +3412,7 @@
         <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3447,7 +3444,7 @@
         <v>115</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3476,7 +3473,7 @@
         <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3505,7 +3502,7 @@
         <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3534,10 +3531,10 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3557,10 +3554,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -3605,10 +3602,10 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3628,10 +3625,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -3676,10 +3673,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3699,10 +3696,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -3801,7 +3798,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3824,7 +3821,7 @@
         <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3847,7 +3844,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3870,7 +3867,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3893,7 +3890,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4053,7 +4050,7 @@
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4076,7 +4073,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4099,7 +4096,7 @@
         <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4160,7 +4157,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>

--- a/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A018AB12-388A-459A-9CBD-C9998C00BAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3746448-8E35-4C11-BDF4-03A68CCED086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="392">
   <si>
     <t>Result</t>
   </si>
@@ -470,9 +470,6 @@
     <t>Fri Jun 05 20:01:44 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 20:02:22 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 20:03:02 EDT 2026</t>
   </si>
   <si>
@@ -617,9 +614,6 @@
     <t>Fri Jun 05 20:46:05 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 20:47:18 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 20:48:31 EDT 2026</t>
   </si>
   <si>
@@ -644,21 +638,9 @@
     <t>Fri Jun 05 20:57:34 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 20:58:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:00:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:01:20 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 21:02:33 EDT 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 21:03:53 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 21:05:06 EDT 2026</t>
   </si>
   <si>
@@ -693,12 +675,559 @@
   </si>
   <si>
     <t>Sat Jun 06 11:31:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:49:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:50:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:50:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:51:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 15:52:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:36:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:37:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:38:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:38:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:39:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:39:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:40:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:40:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:41:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:41:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:42:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:43:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:43:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:44:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:45:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:46:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:47:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:47:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:48:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:48:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:49:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:50:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:51:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:51:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:52:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:53:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:53:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:54:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:54:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:55:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:56:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:56:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:57:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:57:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:58:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:59:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:59:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:00:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:00:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:01:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:02:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:02:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:03:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:04:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:05:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:06:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:06:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:07:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:08:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:08:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:09:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:09:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:10:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:11:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:11:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:12:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:12:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:13:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:14:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:14:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:15:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:15:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:16:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:17:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:17:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:18:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:18:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:19:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:20:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:20:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:21:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:21:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:22:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:23:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:23:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:24:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:24:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:25:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:26:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:26:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:27:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:27:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:28:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:29:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:29:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:30:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:30:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:31:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:32:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:32:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:33:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:33:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:34:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:35:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:35:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:36:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:37:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:37:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:38:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:38:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:39:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:40:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:40:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:41:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:41:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:42:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:43:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:43:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:44:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:45:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:46:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:46:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:47:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:47:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:48:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:49:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:49:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:50:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:50:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:51:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:52:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:52:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:53:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:53:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:54:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:55:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:55:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:56:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:56:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:57:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:58:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:58:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:59:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:59:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:00:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:01:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:01:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:02:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:02:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:03:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:04:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:04:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:05:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:05:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:06:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:07:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:07:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:08:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:08:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:09:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:10:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:10:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:11:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:11:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:13:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:13:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:14:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:15:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:15:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:16:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:16:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:17:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:18:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:18:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:19:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:20:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:20:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:21:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:22:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:22:49 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1071,17 +1600,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1117,11 +1646,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1146,11 +1675,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1175,11 +1704,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1207,11 +1736,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>119</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1239,11 +1768,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1271,11 +1800,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1303,11 +1832,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1340,16 +1869,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1385,11 +1914,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1408,11 +1937,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1431,11 +1960,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1454,11 +1983,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1480,11 +2009,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>127</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1506,11 +2035,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>128</v>
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1529,11 +2058,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>129</v>
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1552,11 +2081,11 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>130</v>
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1575,11 +2104,11 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" t="s">
-        <v>131</v>
+      <c r="A10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1598,11 +2127,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" t="s">
-        <v>132</v>
+      <c r="A11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1621,11 +2150,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" t="s">
-        <v>133</v>
+      <c r="A12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1644,11 +2173,11 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>134</v>
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1667,11 +2196,11 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>135</v>
+      <c r="A14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1690,11 +2219,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
+      <c r="A15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1710,11 +2239,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" t="s">
-        <v>137</v>
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1736,11 +2265,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>138</v>
+      <c r="A17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1759,11 +2288,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s">
-        <v>139</v>
+      <c r="A18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1782,8 +2311,6 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19"/>
-      <c r="B19"/>
       <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,11 +2328,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" t="s">
-        <v>140</v>
+      <c r="A20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1821,14 +2348,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>141</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>107</v>
@@ -1856,15 +2377,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1897,11 +2418,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>142</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1923,11 +2444,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>143</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1946,11 +2467,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>144</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1972,11 +2493,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>145</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1998,11 +2519,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>146</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2024,11 +2545,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>147</v>
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2060,22 +2581,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2107,18 +2629,21 @@
         <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>148</v>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2132,16 +2657,16 @@
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>149</v>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2158,16 +2683,16 @@
       <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>150</v>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2184,16 +2709,16 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>151</v>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2210,16 +2735,16 @@
       <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>152</v>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2236,16 +2761,16 @@
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>153</v>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2259,16 +2784,16 @@
       <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>154</v>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2285,16 +2810,16 @@
       <c r="G8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>155</v>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2311,16 +2836,16 @@
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" t="s">
-        <v>156</v>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2337,16 +2862,16 @@
       <c r="G10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" t="s">
-        <v>157</v>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2363,16 +2888,16 @@
       <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" t="s">
-        <v>158</v>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2386,16 +2911,16 @@
       <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>159</v>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2412,16 +2937,16 @@
       <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>160</v>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2438,16 +2963,16 @@
       <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" t="s">
-        <v>210</v>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2464,16 +2989,16 @@
       <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" t="s">
-        <v>161</v>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2490,16 +3015,16 @@
       <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>162</v>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2519,16 +3044,16 @@
       <c r="I17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s">
-        <v>163</v>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2548,16 +3073,16 @@
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" t="s">
-        <v>164</v>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2577,16 +3102,16 @@
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" t="s">
-        <v>165</v>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2600,16 +3125,16 @@
       <c r="F20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>166</v>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2629,16 +3154,16 @@
       <c r="J21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>167</v>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2658,16 +3183,16 @@
       <c r="I22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B23" t="s">
-        <v>168</v>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2684,16 +3209,16 @@
       <c r="H23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B24" t="s">
-        <v>169</v>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2713,16 +3238,16 @@
       <c r="I24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" t="s">
-        <v>170</v>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2745,16 +3270,16 @@
       <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" t="s">
-        <v>171</v>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2774,16 +3299,16 @@
       <c r="I26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" t="s">
-        <v>172</v>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2803,16 +3328,16 @@
       <c r="H27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2832,19 +3357,19 @@
       <c r="I28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" t="s">
-        <v>174</v>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2864,16 +3389,16 @@
       <c r="I29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" t="s">
-        <v>175</v>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2893,16 +3418,16 @@
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" t="s">
-        <v>176</v>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2922,16 +3447,16 @@
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" t="s">
-        <v>177</v>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2945,16 +3470,16 @@
       <c r="F32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" t="s">
-        <v>178</v>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -2974,16 +3499,16 @@
       <c r="J33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" t="s">
-        <v>179</v>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3003,16 +3528,16 @@
       <c r="I34" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" t="s">
-        <v>180</v>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3029,16 +3554,16 @@
       <c r="H35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" t="s">
-        <v>181</v>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3058,16 +3583,16 @@
       <c r="I36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>182</v>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3090,16 +3615,16 @@
       <c r="I37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" t="s">
-        <v>183</v>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3119,16 +3644,16 @@
       <c r="I38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" t="s">
-        <v>184</v>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3148,16 +3673,16 @@
       <c r="H39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>185</v>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3177,19 +3702,19 @@
       <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" t="s">
-        <v>186</v>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3209,16 +3734,16 @@
       <c r="I41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B42" t="s">
-        <v>187</v>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3238,16 +3763,16 @@
       <c r="I42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>188</v>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3267,16 +3792,16 @@
       <c r="I43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>189</v>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3290,16 +3815,16 @@
       <c r="F44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" t="s">
-        <v>190</v>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3319,16 +3844,16 @@
       <c r="J45" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>115</v>
-      </c>
-      <c r="B46" t="s">
-        <v>191</v>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3348,16 +3873,16 @@
       <c r="I46" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" t="s">
-        <v>192</v>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3374,16 +3899,16 @@
       <c r="H47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" t="s">
-        <v>193</v>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3403,16 +3928,16 @@
       <c r="I48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" t="s">
-        <v>194</v>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3435,16 +3960,16 @@
       <c r="I49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" t="s">
-        <v>195</v>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3464,16 +3989,16 @@
       <c r="I50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" t="s">
-        <v>196</v>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3493,16 +4018,16 @@
       <c r="H51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" t="s">
-        <v>197</v>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3522,19 +4047,19 @@
       <c r="I52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" t="s">
-        <v>198</v>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3548,19 +4073,13 @@
       <c r="F53" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" t="s">
-        <v>199</v>
-      </c>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>15</v>
@@ -3574,13 +4093,11 @@
       <c r="G54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A55"/>
-      <c r="B55"/>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
         <v>32</v>
       </c>
@@ -3600,12 +4117,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" t="s">
-        <v>200</v>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3619,19 +4136,13 @@
       <c r="F56" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" t="s">
-        <v>201</v>
-      </c>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -3645,13 +4156,11 @@
       <c r="G57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A58"/>
-      <c r="B58"/>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
         <v>32</v>
       </c>
@@ -3671,12 +4180,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" t="s">
-        <v>202</v>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3690,19 +4199,13 @@
       <c r="F59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" t="s">
-        <v>203</v>
-      </c>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C60" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -3716,13 +4219,11 @@
       <c r="G60" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A61"/>
-      <c r="B61"/>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
         <v>32</v>
       </c>
@@ -3740,6 +4241,84 @@
       </c>
       <c r="I61" s="1" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>380</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3757,14 +4336,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3794,11 +4373,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>205</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3817,11 +4396,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>206</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3840,11 +4419,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3863,11 +4442,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>208</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3886,11 +4465,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>209</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -3909,8 +4488,6 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7"/>
-      <c r="B7"/>
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
@@ -3925,8 +4502,6 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8"/>
-      <c r="B8"/>
       <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
@@ -3941,8 +4516,6 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9"/>
-      <c r="B9"/>
       <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
@@ -3966,14 +4539,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4000,11 +4573,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>211</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4023,11 +4596,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>212</v>
+      <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4046,11 +4619,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" t="s">
-        <v>215</v>
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4069,11 +4642,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>213</v>
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4092,11 +4665,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>214</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4124,12 +4697,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4153,11 +4726,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>204</v>
+      <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4173,8 +4746,6 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3"/>
-      <c r="B3"/>
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>

--- a/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3746448-8E35-4C11-BDF4-03A68CCED086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6AB31B-4F5B-4A53-A12A-1F2A9F6D9AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="3413" yWindow="3742" windowWidth="21599" windowHeight="11326" activeTab="4" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
   <si>
     <t>Result</t>
   </si>
@@ -395,309 +395,12 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fri Jun 05 19:45:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:45:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:46:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:47:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:47:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:48:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:48:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:49:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:50:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:51:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:51:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:52:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:53:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:54:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:54:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:55:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:56:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:56:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:57:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:58:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:59:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 19:59:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:00:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:01:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:01:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:03:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:03:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:04:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:05:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:05:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:06:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:07:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:08:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:08:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:09:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:09:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:10:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:11:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:12:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:12:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:13:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:14:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:14:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:15:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:16:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:17:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:18:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:19:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:19:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:20:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:21:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:21:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:22:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:22:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:23:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:24:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:25:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:26:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:28:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:29:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:30:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:31:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:33:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:34:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:35:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:36:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:38:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:39:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:40:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:42:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:43:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:44:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:46:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:48:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:49:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:51:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:52:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:53:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:55:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:56:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 20:57:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:02:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:05:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:06:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:08:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:09:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:11:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 21:12:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:20:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:27:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:28:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:29:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:30:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat Jun 06 11:31:37 EDT 2026</t>
-  </si>
-  <si>
     <t>MFInsNum</t>
   </si>
   <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
-    <t>Fri Jul 10 15:49:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:50:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:50:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:51:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 15:52:02 EDT 2026</t>
-  </si>
-  <si>
     <t>Sun Jul 12 00:36:43 EDT 2026</t>
   </si>
   <si>
@@ -719,515 +422,307 @@
     <t>Sun Jul 12 00:39:41 EDT 2026</t>
   </si>
   <si>
-    <t>Sun Jul 12 00:40:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:40:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:41:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:41:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:42:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:43:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:43:48 EDT 2026</t>
+    <t>Sun Jul 12 00:52:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:53:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:53:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:54:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:54:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:55:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:56:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:56:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:57:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:57:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:58:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:59:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 00:59:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:00:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:00:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:01:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:02:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:02:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:03:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:04:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:05:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:06:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:06:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:41:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:42:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:43:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:43:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:44:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:45:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:46:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:46:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:47:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:47:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:48:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:49:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:49:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:50:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:50:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:51:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:52:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:52:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:53:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:53:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:54:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:55:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:55:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:56:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:56:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:57:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:58:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:58:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:59:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 01:59:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:00:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:01:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:01:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:02:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:02:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:03:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:04:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:04:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:05:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:05:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:06:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:07:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:07:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:08:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:08:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:09:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:10:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:10:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:11:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:11:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:13:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:13:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:14:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:15:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:15:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:16:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:16:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:17:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:18:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:18:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:19:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:20:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:20:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:21:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:22:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Jul 12 02:22:49 EDT 2026</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Sun Jul 12 00:44:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:45:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:46:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:47:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:47:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:48:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:48:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:49:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:50:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:51:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:51:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:52:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:53:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:53:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:54:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:54:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:55:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:56:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:56:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:57:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:57:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:58:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:59:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 00:59:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:00:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:00:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:01:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:02:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:02:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:03:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:04:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:04:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:05:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:06:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:06:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:07:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:08:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:08:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:09:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:09:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:10:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:11:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:11:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:12:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:12:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:13:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:14:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:14:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:15:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:15:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:16:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:17:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:17:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:18:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:18:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:19:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:20:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:20:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:21:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:21:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:22:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:23:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:23:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:24:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:24:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:25:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:26:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:26:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:27:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:27:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:28:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:29:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:29:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:30:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:30:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:31:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:32:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:32:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:33:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:33:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:34:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:35:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:35:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:36:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:37:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:37:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:38:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:38:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:39:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:40:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:40:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:41:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:41:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:42:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:43:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:43:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:44:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:44:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:45:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:46:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:46:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:47:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:47:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:48:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:49:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:49:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:50:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:50:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:51:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:52:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:52:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:53:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:53:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:54:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:55:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:55:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:56:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:56:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:57:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:58:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:58:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:59:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 01:59:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:00:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:01:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:01:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:02:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:02:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:03:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:04:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:04:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:05:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:05:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:06:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:07:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:07:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:08:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:08:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:09:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:10:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:10:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:11:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:11:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:12:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:13:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:13:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:14:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:15:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:15:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:16:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:16:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:17:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:18:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:18:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:19:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:20:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:20:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:21:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:22:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Jul 12 02:22:49 EDT 2026</t>
+    <t>Sun Aug 02 14:22:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:23:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 14:24:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:28:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:30:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:31:02 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1600,17 +1095,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1650,7 +1145,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1679,7 +1174,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1708,7 +1203,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1740,7 +1235,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1772,7 +1267,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>221</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1804,7 +1299,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1836,7 +1331,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1869,16 +1364,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1918,7 +1413,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>243</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1941,7 +1436,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1964,7 +1459,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1987,7 +1482,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>246</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2013,7 +1508,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>247</v>
+        <v>129</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2039,7 +1534,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>248</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2062,7 +1557,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2085,7 +1580,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2108,7 +1603,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2131,7 +1626,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2154,7 +1649,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2177,7 +1672,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2200,7 +1695,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>255</v>
+        <v>137</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2223,7 +1718,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>256</v>
+        <v>138</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2243,7 +1738,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2269,7 +1764,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2292,7 +1787,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>259</v>
+        <v>141</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2332,7 +1827,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2377,15 +1872,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2422,7 +1917,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>261</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2448,7 +1943,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>262</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2471,7 +1966,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2497,7 +1992,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2523,7 +2018,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2549,7 +2044,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>266</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2584,17 +2079,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
-    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
-    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
+    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2629,7 +2124,7 @@
         <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>43</v>
@@ -2643,7 +2138,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>324</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2666,7 +2161,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2692,7 +2187,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>326</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2718,7 +2213,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>327</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2744,7 +2239,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>328</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2770,7 +2265,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>329</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2793,7 +2288,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>330</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2819,7 +2314,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>331</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2845,7 +2340,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>332</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2871,7 +2366,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>333</v>
+        <v>158</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2897,7 +2392,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>334</v>
+        <v>159</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2920,7 +2415,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>335</v>
+        <v>160</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2946,7 +2441,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2972,7 +2467,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2998,7 +2493,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -3024,7 +2519,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>339</v>
+        <v>164</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -3053,7 +2548,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -3082,7 +2577,7 @@
         <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>341</v>
+        <v>166</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -3111,7 +2606,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>342</v>
+        <v>167</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -3134,7 +2629,7 @@
         <v>115</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>343</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -3163,7 +2658,7 @@
         <v>115</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>344</v>
+        <v>169</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -3192,7 +2687,7 @@
         <v>115</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>345</v>
+        <v>170</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -3218,7 +2713,7 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>346</v>
+        <v>171</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -3247,7 +2742,7 @@
         <v>115</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>347</v>
+        <v>172</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -3279,7 +2774,7 @@
         <v>115</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>348</v>
+        <v>173</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -3308,7 +2803,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>349</v>
+        <v>174</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -3337,7 +2832,7 @@
         <v>115</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -3369,7 +2864,7 @@
         <v>115</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>351</v>
+        <v>176</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -3398,7 +2893,7 @@
         <v>115</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>352</v>
+        <v>177</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -3427,7 +2922,7 @@
         <v>115</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>353</v>
+        <v>178</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -3456,7 +2951,7 @@
         <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>354</v>
+        <v>179</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -3479,7 +2974,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>355</v>
+        <v>180</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3508,7 +3003,7 @@
         <v>115</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>356</v>
+        <v>181</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3537,7 +3032,7 @@
         <v>115</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3563,7 +3058,7 @@
         <v>115</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>358</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3592,7 +3087,7 @@
         <v>115</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>359</v>
+        <v>184</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3624,7 +3119,7 @@
         <v>115</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3653,7 +3148,7 @@
         <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>361</v>
+        <v>186</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3682,7 +3177,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>362</v>
+        <v>187</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3714,7 +3209,7 @@
         <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>363</v>
+        <v>188</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3743,7 +3238,7 @@
         <v>115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>364</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3772,7 +3267,7 @@
         <v>115</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>365</v>
+        <v>190</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3801,7 +3296,7 @@
         <v>115</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>366</v>
+        <v>191</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3824,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>367</v>
+        <v>192</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3853,7 +3348,7 @@
         <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>368</v>
+        <v>193</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3882,7 +3377,7 @@
         <v>115</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>369</v>
+        <v>194</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3908,7 +3403,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>370</v>
+        <v>195</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3937,7 +3432,7 @@
         <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>371</v>
+        <v>196</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3969,7 +3464,7 @@
         <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>372</v>
+        <v>197</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3998,7 +3493,7 @@
         <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -4027,7 +3522,7 @@
         <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>374</v>
+        <v>199</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -4059,7 +3554,7 @@
         <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -4078,8 +3573,14 @@
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>15</v>
@@ -4122,7 +3623,7 @@
         <v>115</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>376</v>
+        <v>201</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -4141,8 +3642,14 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -4185,7 +3692,7 @@
         <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>377</v>
+        <v>202</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -4204,8 +3711,14 @@
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -4248,7 +3761,7 @@
         <v>115</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>378</v>
+        <v>203</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -4257,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>114</v>
@@ -4274,7 +3787,7 @@
         <v>115</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>379</v>
+        <v>204</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -4283,7 +3796,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>109</v>
@@ -4299,8 +3812,8 @@
       <c r="A64" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B64" t="s" s="1">
-        <v>380</v>
+      <c r="B64" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -4309,7 +3822,7 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>33</v>
@@ -4336,14 +3849,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4377,7 +3890,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>382</v>
+        <v>207</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4400,7 +3913,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>383</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4423,7 +3936,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>384</v>
+        <v>209</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4446,7 +3959,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>385</v>
+        <v>210</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4469,7 +3982,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>386</v>
+        <v>211</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4488,8 +4001,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -4498,12 +4017,18 @@
         <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -4512,12 +4037,18 @@
         <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>223</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
@@ -4526,7 +4057,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4539,14 +4070,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4577,7 +4108,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4600,7 +4131,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>388</v>
+        <v>213</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4623,7 +4154,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>389</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4646,7 +4177,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>390</v>
+        <v>215</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4669,7 +4200,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>391</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4697,12 +4228,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4730,7 +4261,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>206</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
